--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -1683,7 +1683,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -1683,7 +1683,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 11/09/2026 — 1º e 2º tempos</t>
+          <t>Sexta, 11/09/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 11º e 12º tempos</t>
+          <t>Terça, 08/09/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Terça, 08/09/2026 — 11º e 12º tempos</t>
+          <t>Terça, 08/09/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -3825,57 +3825,57 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
+          <t>Quinta, 22/10/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -3885,17 +3885,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 5º e 6º tempos</t>
+          <t>Segunda, 26/10/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -3905,37 +3905,37 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 2º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 5º e 6º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -3945,17 +3945,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 2º tempo</t>
+          <t>Quarta, 04/11/2026 — 10º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -3965,17 +3965,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 05/11/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -3985,21 +3985,21 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 10º tempo</t>
+          <t>Sexta, 06/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -4358,57 +4358,57 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 01/10/2026 — 9º e 10º tempos</t>
+          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 1º ao 3º tempos</t>
+          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Terça, 20/10/2026 — 10º e 11º tempos</t>
+          <t>Quinta, 22/10/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -4418,17 +4418,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 22/10/2026 — 5º e 6º tempos</t>
+          <t>Segunda, 26/10/2026 — 5º e 6º tempos</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -4438,37 +4438,37 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 23/10/2026 — 6º e 7º tempos</t>
+          <t>Quarta, 28/10/2026 — 6º tempo</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 5º e 6º tempos</t>
+          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -4478,17 +4478,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 28/10/2026 — 6º tempo</t>
+          <t>Quarta, 04/11/2026 — 4º tempo</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -4498,17 +4498,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 05/11/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -4518,21 +4518,21 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Quarta, 04/11/2026 — 4º tempo</t>
+          <t>Sexta, 06/11/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -977,7 +977,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 24/11/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quinta, 19/11/2026 — 4º e 5º tempos</t>
+          <t>Terça, 24/11/2026 — 9º e 10º tempos</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">

--- a/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
+++ b/Horario desenvolvido/Tabela_Provas_por_Turma_Proposta_3.xlsx
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Segunda, 26/10/2026 — 4º e 5º tempos</t>
+          <t>Terça, 27/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Quinta, 29/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 29/10/2026 — 6º e 7º tempos</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sexta, 09/10/2026 — 2º e 3º tempos</t>
+          <t>Quinta, 08/10/2026 — 1º e 2º tempos</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
